--- a/c5/downloads/C5/SkyG-Speed-60-BOM.xlsx
+++ b/c5/downloads/C5/SkyG-Speed-60-BOM.xlsx
@@ -2734,7 +2734,7 @@
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>Nylon screw M3 x 12</t>
+          <t>Nylon screw M3 x 8</t>
         </is>
       </c>
       <c r="D53" s="4" t="n">
@@ -2745,12 +2745,12 @@
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>Nylon PA66 socket or pan head</t>
+          <t>Nylon PA66 pan head</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>M3x12 nylon screw</t>
+          <t>M3x8 nylon screw</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>A 16 mm screw here reaches the aileron servo</t>
+          <t>A 12 mm screw here reaches the aileron servo arm (found with the screws modelled in the assembly)</t>
         </is>
       </c>
     </row>
@@ -3765,7 +3765,7 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>17.2</v>
+        <v>17.3</v>
       </c>
       <c r="D15" s="4" t="n">
         <v>1.89</v>
@@ -4120,7 +4120,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>One aircraft (one aircraft with the N0M nose; N0P is an alternative part): 107.3 g, 15.6 h of printing.</t>
+          <t>One aircraft (one aircraft with the N0M nose; N0P is an alternative part): 107.4 g, 15.6 h of printing.</t>
         </is>
       </c>
     </row>

--- a/c5/downloads/C5/SkyG-Speed-60-BOM.xlsx
+++ b/c5/downloads/C5/SkyG-Speed-60-BOM.xlsx
@@ -1438,7 +1438,7 @@
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Nylon screw M3 x 16</t>
+          <t>Nylon countersunk screw M3 x 16</t>
         </is>
       </c>
       <c r="D24" s="7" t="n">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="F24" s="8" t="inlineStr">
         <is>
-          <t>Nylon PA66 socket or pan head</t>
+          <t>Nylon PA66 countersunk (flat head, DIN 965 / ISO 7046)</t>
         </is>
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t>M3x16 nylon screws</t>
+          <t>M3x16 nylon countersunk screw</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>M2 x 6 screws</t>
+          <t>M2 x 6 countersunk screws (joints)</t>
         </is>
       </c>
       <c r="D26" s="7" t="n">
@@ -1537,17 +1537,17 @@
       </c>
       <c r="F26" s="8" t="inlineStr">
         <is>
-          <t>Steel socket/pan head</t>
+          <t>M2 x 6 countersunk (DIN 965), steel</t>
         </is>
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>M2x6 screws</t>
+          <t>M2x6 countersunk screws</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>Fuselage joints (3 x 2), into internal bosses (4.5 mm thread)</t>
+          <t>Fuselage joints (3 x 2), flush in countersinks in the skin, into internal bosses (4.5 mm thread)</t>
         </is>
       </c>
       <c r="I26" s="7" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>Nylon screw M3 x 8</t>
+          <t>Nylon countersunk screw M3 x 8</t>
         </is>
       </c>
       <c r="D53" s="4" t="n">
@@ -2745,12 +2745,12 @@
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>Nylon PA66 pan head</t>
+          <t>Nylon PA66 countersunk (flat head, DIN 965 / ISO 7046)</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>M3x8 nylon screw</t>
+          <t>M3x8 nylon countersunk screw</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
@@ -3765,7 +3765,7 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>17.3</v>
+        <v>17.2</v>
       </c>
       <c r="D15" s="4" t="n">
         <v>1.89</v>
@@ -3791,10 +3791,10 @@
         </is>
       </c>
       <c r="C16" s="7" t="n">
-        <v>20.8</v>
+        <v>20.6</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="E16" s="7" t="n">
         <v>2</v>
@@ -3817,10 +3817,10 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="E17" s="4" t="n">
         <v>2</v>
@@ -4120,7 +4120,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>One aircraft (one aircraft with the N0M nose; N0P is an alternative part): 107.4 g, 15.6 h of printing.</t>
+          <t>One aircraft (one aircraft with the N0M nose; N0P is an alternative part): 107.0 g, 15.6 h of printing.</t>
         </is>
       </c>
     </row>
